--- a/output/LP SOLUTION.xlsx
+++ b/output/LP SOLUTION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\AD OPTIMIZATION\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30D268E5-C6C9-4838-95AA-21780B100CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5992B5CD-F85E-4CDD-864A-923D2764D1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D87936BB-2E30-45BB-A295-4D66BFE55BD2}"/>
   </bookViews>
@@ -34,7 +34,6 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">4</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$B$15</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
@@ -66,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>AD BUDGET ALLOCATION-LP</t>
   </si>
@@ -123,13 +122,68 @@
   </si>
   <si>
     <t>Newspaper Maximum</t>
+  </si>
+  <si>
+    <t>Baseline vs Optimized Allocation</t>
+  </si>
+  <si>
+    <t>Baseline Spend ($000s)</t>
+  </si>
+  <si>
+    <t>Baseline Share (%)</t>
+  </si>
+  <si>
+    <t>Optimized Share (%)</t>
+  </si>
+  <si>
+    <t>Change (000s)</t>
+  </si>
+  <si>
+    <t>Change (%)</t>
+  </si>
+  <si>
+    <t>Optimized Spend (000s)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Newspaper</t>
+  </si>
+  <si>
+    <t>Radio</t>
+  </si>
+  <si>
+    <t>Baseline vs Optimized Performance</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Optimized</t>
+  </si>
+  <si>
+    <t>Improvement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Improvement (%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,27 +193,26 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,6 +231,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -188,34 +259,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -527,163 +605,364 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E86799-1283-4E92-AB59-FC65FBEBE413}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" customWidth="1"/>
-    <col min="3" max="3" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="40.453125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="41.08984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.453125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.5">
+      <c r="D1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <v>151.26050000000001</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>5.4449999999999998E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="4">
         <v>49.6</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="3">
         <v>0.107</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="4">
         <v>0</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="3">
         <v>3.4000000000000002E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>SUM(B5:B7)</f>
         <v>200.8605</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>4.6250999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="7">
         <f>B5*C5</f>
         <v>8.2361342250000007</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="8">
         <f>B6*C6</f>
         <v>5.3071999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="8">
         <f>B7*C7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="3">
-        <f>B11+ SUM(B12:B14)</f>
+      <c r="B15" s="2">
+        <f>B11+SUM(B12:B14)</f>
         <v>18.168434224999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>200.8605</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="3">
         <v>296.39999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>49.6</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="6">
+        <v>147.04249999999999</v>
+      </c>
+      <c r="C26" s="9">
+        <f>B26/$B$29</f>
+        <v>0.73206279980384392</v>
+      </c>
+      <c r="D26" s="3">
+        <v>151.26050000000001</v>
+      </c>
+      <c r="E26" s="9">
+        <f>D26/$D$29</f>
+        <v>0.75306244881397788</v>
+      </c>
+      <c r="F26" s="10">
+        <f>D26-B26</f>
+        <v>4.2180000000000177</v>
+      </c>
+      <c r="G26" s="11">
+        <f>(D26-B26)/B26</f>
+        <v>2.8685584099835203E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3">
+        <v>23.263999999999999</v>
+      </c>
+      <c r="C27" s="9">
+        <f t="shared" ref="C27:C28" si="0">B27/$B$29</f>
+        <v>0.11582167723370199</v>
+      </c>
+      <c r="D27" s="3">
+        <v>49.6</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" ref="E27:E28" si="1">D27/$D$29</f>
+        <v>0.24693755118602215</v>
+      </c>
+      <c r="F27" s="10">
+        <f t="shared" ref="F27:F28" si="2">D27-B27</f>
+        <v>26.336000000000002</v>
+      </c>
+      <c r="G27" s="11">
+        <f t="shared" ref="G27:G28" si="3">(D27-B27)/B27</f>
+        <v>1.1320495185694637</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>30.553999999999998</v>
+      </c>
+      <c r="C28" s="9">
+        <f t="shared" si="0"/>
+        <v>0.15211552296245404</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="10">
+        <f t="shared" si="2"/>
+        <v>-30.553999999999998</v>
+      </c>
+      <c r="G28" s="11">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2">
+        <v>200.8605</v>
+      </c>
+      <c r="C29" s="12">
+        <f>SUM(C26:C28)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="D29" s="3">
+        <f>SUM(D26:D28)</f>
+        <v>200.8605</v>
+      </c>
+      <c r="E29" s="12">
+        <f>SUM(E26:E28)</f>
+        <v>1</v>
+      </c>
+      <c r="F29" s="10">
+        <f>SUM(F26:F28)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="53" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="3">
+        <f>$B$11+($B$26*$C$5)+($B$27*$C$6)+($B$28*$C$7)</f>
+        <v>15.131200484999999</v>
+      </c>
+      <c r="C34" s="3">
+        <f>$B$15</f>
+        <v>18.168434224999999</v>
+      </c>
+      <c r="D34" s="13">
+        <f>C34-B34</f>
+        <v>3.0372337399999996</v>
+      </c>
+      <c r="E34" s="14">
+        <f>(C34-B34)/B34</f>
+        <v>0.20072655457912267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="2">
+        <v>200.8605</v>
+      </c>
+      <c r="C35" s="3">
+        <v>200.8605</v>
+      </c>
+      <c r="D35" s="13">
+        <f>C35-B35</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
